--- a/Padrao/Leiautes/Tabela de Preços/Tabelas Genericas/PRESTADOR/Tabela Generica/Relação Tabela Generica - Prestador.xlsx
+++ b/Padrao/Leiautes/Tabela de Preços/Tabelas Genericas/PRESTADOR/Tabela Generica/Relação Tabela Generica - Prestador.xlsx
@@ -13,9 +13,8 @@
   </bookViews>
   <sheets>
     <sheet name="SAM_PRECOPRESTADOR_VIG" sheetId="1" r:id="rId1"/>
-    <sheet name="SAM_PRECOPRESTADOR_TAB" sheetId="2" r:id="rId2"/>
-    <sheet name="Tabela de Filme" sheetId="3" r:id="rId3"/>
-    <sheet name="Tabela de Custo Operacional" sheetId="4" r:id="rId4"/>
+    <sheet name="Tabela de Filme" sheetId="3" r:id="rId2"/>
+    <sheet name="Tabela de Custo Operacional" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -27,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="99">
   <si>
     <t>TABELA</t>
   </si>
@@ -183,12 +182,6 @@
   </si>
   <si>
     <t>Percentual de pagamento para a US de honorários</t>
-  </si>
-  <si>
-    <t>PRECOPRESTADORVIG</t>
-  </si>
-  <si>
-    <t>Vigência</t>
   </si>
   <si>
     <t>TABELACUSTOOPERAC</t>
@@ -666,9 +659,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="20.33203125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="35.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -875,7 +869,7 @@
         <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -904,7 +898,7 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -1011,16 +1005,16 @@
         <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1028,10 +1022,10 @@
         <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -1046,10 +1040,10 @@
         <v>15</v>
       </c>
       <c r="I13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1057,7 +1051,7 @@
         <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
         <v>58</v>
@@ -1069,16 +1063,16 @@
         <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>59</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>97</v>
+        <v>21</v>
+      </c>
+      <c r="L14" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -1086,7 +1080,7 @@
         <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
         <v>60</v>
@@ -1098,51 +1092,22 @@
         <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
       </c>
       <c r="I15" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="L15" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16">
-        <v>6</v>
-      </c>
-      <c r="E16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L13" location="'Tabela de Custo Operacional'!A1" display="Informe o valor da coluna handle Tabela de custo operacional"/>
-    <hyperlink ref="L14" location="'Tabela de Filme'!A1" display="Informe o valor da coluna Handle da Tabela de Filme da planilha Tabela de Filmee"/>
+    <hyperlink ref="L12" location="'Tabela de Custo Operacional'!A1" display="Informe o valor da coluna handle Tabela de custo operacional"/>
+    <hyperlink ref="L13" location="'Tabela de Filme'!A1" display="Informe o valor da coluna Handle da Tabela de Filme da planilha Tabela de Filmee"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1151,345 +1116,114 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="36.6640625" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B5" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="L3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4">
-        <v>5</v>
-      </c>
-      <c r="L4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="L5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="L6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8">
-        <v>6</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9">
-        <v>6</v>
-      </c>
-      <c r="E9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10">
-        <v>6</v>
-      </c>
-      <c r="E10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" t="s">
-        <v>63</v>
-      </c>
-      <c r="L11" t="s">
-        <v>99</v>
+      <c r="B10" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="L8" location="'Tabela de Custo Operacional'!A1" display="Informe o valor da coluna handle Tabela de custo operacional"/>
-    <hyperlink ref="L9" location="'Tabela de Filme'!A1" display="Informe o valor da coluna Handle da Tabela de Filme da planilha Tabela de Filmee"/>
-  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1497,130 +1231,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>12</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1628,7 +1247,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1636,7 +1255,7 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -1644,7 +1263,7 @@
         <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -1652,7 +1271,7 @@
         <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1660,7 +1279,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1668,7 +1287,7 @@
         <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -1676,7 +1295,7 @@
         <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1684,7 +1303,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1692,7 +1311,7 @@
         <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1700,7 +1319,7 @@
         <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1708,7 +1327,7 @@
         <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -1716,7 +1335,7 @@
         <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -1724,7 +1343,7 @@
         <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -1732,7 +1351,7 @@
         <v>99</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -1740,7 +1359,7 @@
         <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -1748,7 +1367,7 @@
         <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1756,7 +1375,7 @@
         <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -1764,7 +1383,7 @@
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -1772,7 +1391,7 @@
         <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -1780,7 +1399,7 @@
         <v>81</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -1788,7 +1407,7 @@
         <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -1796,7 +1415,7 @@
         <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -1804,7 +1423,7 @@
         <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
